--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -93,7 +93,7 @@
     <t>主菜单</t>
   </si>
   <si>
-    <t>res://TheGame/UI/MainMenu.tscn</t>
+    <t>res://TheGame/UIs/MenuForm.tscn</t>
   </si>
   <si>
     <t>Normal</t>
@@ -102,7 +102,7 @@
     <t>游戏界面</t>
   </si>
   <si>
-    <t>res://TheGame/UI/GameHUD.tscn</t>
+    <t>res://TheGame/UIs/MainForm.tscn</t>
   </si>
 </sst>
 </file>

--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="27930" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -104,16 +104,22 @@
   <si>
     <t>res://TheGame/UIs/MainForm.tscn</t>
   </si>
+  <si>
+    <t>设置界面</t>
+  </si>
+  <si>
+    <t>res://TheGame/UIs/SettingForm.tscn</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -621,19 +627,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1116,7 +1122,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
@@ -1397,6 +1403,18 @@
       <c r="N7" s="13"/>
     </row>
     <row r="8" spans="1:36">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="J8" s="12"/>
       <c r="L8" s="12"/>

--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27930" windowHeight="12975"/>
+    <workbookView windowWidth="25600" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -110,16 +110,22 @@
   <si>
     <t>res://TheGame/UIs/SettingForm.tscn</t>
   </si>
+  <si>
+    <t>结束界面</t>
+  </si>
+  <si>
+    <t>res://TheGame/UIs/GameOver.tscn</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -627,19 +633,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1122,7 +1128,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AJ15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
@@ -1422,6 +1428,18 @@
       <c r="N8" s="13"/>
     </row>
     <row r="9" spans="1:36">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
       <c r="H9" s="12"/>
       <c r="J9" s="12"/>
       <c r="L9" s="12"/>

--- a/Configs/GameConfig/Datas/界面UI.xlsx
+++ b/Configs/GameConfig/Datas/界面UI.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -60,6 +60,9 @@
     <t>AssetPath</t>
   </si>
   <si>
+    <t>pauseCoveredUIForm</t>
+  </si>
+  <si>
     <t>UIGroupName</t>
   </si>
   <si>
@@ -72,6 +75,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
   </si>
   <si>
     <t>资源名</t>
+  </si>
+  <si>
+    <t>遮挡是否暂停</t>
   </si>
   <si>
     <t>处于哪个组</t>
@@ -1127,26 +1136,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="6.75" customWidth="1"/>
     <col min="3" max="3" width="21.6666666666667" customWidth="1"/>
     <col min="4" max="4" width="48.1666666666667" customWidth="1"/>
-    <col min="5" max="5" width="12.3833333333333" customWidth="1"/>
-    <col min="6" max="6" width="5.5" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
-    <col min="8" max="8" width="16.5" customWidth="1"/>
-    <col min="9" max="9" width="13.1333333333333" customWidth="1"/>
-    <col min="10" max="10" width="12.3833333333333" customWidth="1"/>
-    <col min="11" max="11" width="17.8833333333333" customWidth="1"/>
-    <col min="12" max="12" width="28" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="5.13333333333333" customWidth="1"/>
+    <col min="5" max="6" width="12.3833333333333" customWidth="1"/>
+    <col min="7" max="7" width="5.5" customWidth="1"/>
+    <col min="8" max="8" width="18.75" customWidth="1"/>
+    <col min="9" max="9" width="16.5" customWidth="1"/>
+    <col min="10" max="10" width="13.1333333333333" customWidth="1"/>
+    <col min="11" max="11" width="12.3833333333333" customWidth="1"/>
+    <col min="12" max="12" width="17.8833333333333" customWidth="1"/>
+    <col min="13" max="13" width="28" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="5.13333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:36">
+    <row r="1" s="1" customFormat="1" spans="1:37">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1162,17 +1171,19 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="6"/>
-      <c r="P1"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="6"/>
       <c r="Q1"/>
       <c r="R1"/>
       <c r="S1"/>
@@ -1193,8 +1204,9 @@
       <c r="AH1"/>
       <c r="AI1"/>
       <c r="AJ1"/>
+      <c r="AK1"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:36">
+    <row r="2" s="1" customFormat="1" spans="1:37">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1209,10 +1221,10 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="6"/>
-      <c r="P2"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="6"/>
       <c r="Q2"/>
       <c r="R2"/>
       <c r="S2"/>
@@ -1233,34 +1245,37 @@
       <c r="AH2"/>
       <c r="AI2"/>
       <c r="AJ2"/>
+      <c r="AK2"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:36">
+    <row r="3" s="2" customFormat="1" spans="1:37">
       <c r="A3" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="8"/>
+        <v>9</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="6"/>
-      <c r="P3"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="6"/>
       <c r="Q3"/>
       <c r="R3"/>
       <c r="S3"/>
@@ -1281,10 +1296,11 @@
       <c r="AH3"/>
       <c r="AI3"/>
       <c r="AJ3"/>
+      <c r="AK3"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:36">
+    <row r="4" s="2" customFormat="1" spans="1:37">
       <c r="A4" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1295,12 +1311,12 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="6"/>
-      <c r="P4"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="6"/>
       <c r="Q4"/>
       <c r="R4"/>
       <c r="S4"/>
@@ -1321,34 +1337,37 @@
       <c r="AH4"/>
       <c r="AI4"/>
       <c r="AJ4"/>
+      <c r="AK4"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:36">
+    <row r="5" s="1" customFormat="1" spans="1:37">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6"/>
-      <c r="P5"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="6"/>
       <c r="Q5"/>
       <c r="R5"/>
       <c r="S5"/>
@@ -1369,139 +1388,155 @@
       <c r="AH5"/>
       <c r="AI5"/>
       <c r="AJ5"/>
+      <c r="AK5"/>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:37">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="13"/>
+        <v>18</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="M6" s="12"/>
       <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
     </row>
-    <row r="7" spans="1:36">
+    <row r="7" spans="1:37">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="13"/>
+        <v>21</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="M7" s="12"/>
       <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
     </row>
-    <row r="8" spans="1:36">
+    <row r="8" spans="1:37">
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="13"/>
+      <c r="I8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="M8" s="12"/>
       <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
     </row>
-    <row r="9" spans="1:36">
+    <row r="9" spans="1:37">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="13"/>
+        <v>25</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="M9" s="12"/>
       <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
     </row>
-    <row r="10" spans="1:36">
-      <c r="H10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="13"/>
+    <row r="10" spans="1:37">
+      <c r="I10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="M10" s="12"/>
       <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
     </row>
-    <row r="11" spans="1:36">
+    <row r="11" spans="1:37">
       <c r="C11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="13"/>
+      <c r="I11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="M11" s="12"/>
       <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
     </row>
-    <row r="12" spans="1:36">
-      <c r="H12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="13"/>
+    <row r="12" spans="1:37">
+      <c r="I12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="M12" s="12"/>
       <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
     </row>
-    <row r="13" spans="1:36">
+    <row r="13" spans="1:37">
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
-      <c r="H13" s="14"/>
-      <c r="J13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="13"/>
+      <c r="F13" s="12"/>
+      <c r="I13" s="14"/>
+      <c r="K13" s="12"/>
+      <c r="M13" s="12"/>
       <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
     </row>
-    <row r="14" spans="1:36">
+    <row r="14" spans="1:37">
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
-      <c r="H14" s="14"/>
-      <c r="J14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="13"/>
+      <c r="F14" s="12"/>
+      <c r="I14" s="14"/>
+      <c r="K14" s="12"/>
+      <c r="M14" s="12"/>
       <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
     </row>
-    <row r="15" spans="1:36">
+    <row r="15" spans="1:37">
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
       <c r="E15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="13"/>
+      <c r="F15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="M15" s="12"/>
       <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
